--- a/companies/sec/model.xlsx
+++ b/companies/sec/model.xlsx
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>07b845a4d0344174</t>
+          <t>945d5955a2316988</t>
         </is>
       </c>
     </row>

--- a/companies/sec/model.xlsx
+++ b/companies/sec/model.xlsx
@@ -7631,7 +7631,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>945d5955a2316988</t>
+          <t>e61fd84cce1d331a</t>
         </is>
       </c>
     </row>
